--- a/CISC691_FA25_A03_Status.xlsx
+++ b/CISC691_FA25_A03_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/donohara/Data/001_HU/_github/hu_2025_classes/110_HU/Classes/05__2025_Fall_CISC_691/20_Class_notes/wk_10_2025_1027/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/051890dcf11f43f2/Desktop/a03_agentic_ai/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D3D4F8-5207-C341-B8C4-41DC3CA519F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{D8D3D4F8-5207-C341-B8C4-41DC3CA519F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6D68FB7-1C1F-42BC-83AC-FFC79090DA56}"/>
   <bookViews>
-    <workbookView xWindow="620" yWindow="900" windowWidth="32560" windowHeight="20120" xr2:uid="{472195A6-5F2D-DC40-A561-3ED564DE870D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{472195A6-5F2D-DC40-A561-3ED564DE870D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="94">
   <si>
     <t>ID</t>
   </si>
@@ -326,13 +326,16 @@
   </si>
   <si>
     <t>IV.4</t>
+  </si>
+  <si>
+    <t>Done</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -855,23 +858,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C90F98-B029-8F41-AF22-27374B28F3FE}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="49.6640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="55.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="79.33203125" style="21" customWidth="1"/>
+    <col min="1" max="1" width="49.69921875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="55.796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.69921875" style="20" customWidth="1"/>
+    <col min="4" max="4" width="79.296875" style="21" customWidth="1"/>
     <col min="5" max="5" width="31.5" style="4" customWidth="1"/>
-    <col min="6" max="6" width="59.1640625" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="4"/>
+    <col min="6" max="6" width="59.19921875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="10.796875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="36">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -891,7 +894,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" s="5" t="s">
         <v>37</v>
       </c>
@@ -904,10 +907,12 @@
       <c r="D3" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="7" t="s">
@@ -916,10 +921,12 @@
       <c r="D4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="7" t="s">
@@ -928,10 +935,12 @@
       <c r="D5" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="36">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
         <v>36</v>
@@ -942,10 +951,12 @@
       <c r="D6" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="36">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7" t="s">
@@ -954,10 +965,12 @@
       <c r="D7" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="6"/>
+      <c r="E7" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="36">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
@@ -966,10 +979,12 @@
       <c r="D8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="36">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
@@ -978,10 +993,12 @@
       <c r="D9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F9" s="6"/>
     </row>
-    <row r="10" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
         <v>38</v>
@@ -992,10 +1009,12 @@
       <c r="D10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="36">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
@@ -1004,10 +1023,12 @@
       <c r="D11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="36">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="7" t="s">
@@ -1016,10 +1037,12 @@
       <c r="D12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F12" s="6"/>
     </row>
-    <row r="13" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
         <v>39</v>
@@ -1030,10 +1053,12 @@
       <c r="D13" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7" t="s">
@@ -1042,10 +1067,12 @@
       <c r="D14" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="6" t="s">
+        <v>93</v>
+      </c>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="36">
       <c r="A15" s="9" t="s">
         <v>40</v>
       </c>
@@ -1058,10 +1085,12 @@
       <c r="D15" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="10"/>
+      <c r="E15" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="F15" s="10"/>
     </row>
-    <row r="16" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="11" t="s">
@@ -1070,10 +1099,12 @@
       <c r="D16" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="10"/>
+      <c r="E16" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="F16" s="10"/>
     </row>
-    <row r="17" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="36">
       <c r="A17" s="10"/>
       <c r="B17" s="10" t="s">
         <v>42</v>
@@ -1084,10 +1115,12 @@
       <c r="D17" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="10"/>
+      <c r="E17" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="F17" s="10"/>
     </row>
-    <row r="18" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
       <c r="C18" s="11" t="s">
@@ -1096,10 +1129,12 @@
       <c r="D18" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="10"/>
+      <c r="E18" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="F18" s="10"/>
     </row>
-    <row r="19" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" s="10"/>
       <c r="B19" s="10"/>
       <c r="C19" s="11" t="s">
@@ -1108,10 +1143,12 @@
       <c r="D19" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="10"/>
+      <c r="E19" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="F19" s="10"/>
     </row>
-    <row r="20" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="11" t="s">
@@ -1120,10 +1157,12 @@
       <c r="D20" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="10"/>
+      <c r="E20" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="F20" s="10"/>
     </row>
-    <row r="21" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" s="10"/>
       <c r="B21" s="10" t="s">
         <v>43</v>
@@ -1134,10 +1173,12 @@
       <c r="D21" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="10"/>
+      <c r="E21" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="F21" s="10"/>
     </row>
-    <row r="22" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="11" t="s">
@@ -1146,10 +1187,12 @@
       <c r="D22" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="10"/>
+      <c r="E22" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="F22" s="10"/>
     </row>
-    <row r="23" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="11" t="s">
@@ -1158,10 +1201,12 @@
       <c r="D23" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E23" s="10"/>
+      <c r="E23" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="F23" s="10"/>
     </row>
-    <row r="24" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" s="13" t="s">
         <v>44</v>
       </c>
@@ -1174,10 +1219,12 @@
       <c r="D24" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="E24" s="14"/>
+      <c r="E24" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="F24" s="14"/>
     </row>
-    <row r="25" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" s="14"/>
       <c r="B25" s="14"/>
       <c r="C25" s="15" t="s">
@@ -1186,10 +1233,12 @@
       <c r="D25" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="E25" s="14"/>
+      <c r="E25" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="F25" s="14"/>
     </row>
-    <row r="26" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="36">
       <c r="A26" s="14"/>
       <c r="B26" s="14" t="s">
         <v>46</v>
@@ -1200,10 +1249,12 @@
       <c r="D26" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="14"/>
+      <c r="E26" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="F26" s="14"/>
     </row>
-    <row r="27" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
       <c r="C27" s="15" t="s">
@@ -1212,10 +1263,12 @@
       <c r="D27" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="14"/>
+      <c r="E27" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="F27" s="14"/>
     </row>
-    <row r="28" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="C28" s="25" t="s">
@@ -1224,10 +1277,12 @@
       <c r="D28" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E28" s="14"/>
+      <c r="E28" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="F28" s="14"/>
     </row>
-    <row r="29" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
       <c r="C29" s="25" t="s">
@@ -1236,10 +1291,12 @@
       <c r="D29" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="14"/>
+      <c r="E29" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="F29" s="14"/>
     </row>
-    <row r="30" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" s="14"/>
       <c r="B30" s="14"/>
       <c r="C30" s="25" t="s">
@@ -1248,10 +1305,12 @@
       <c r="D30" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="E30" s="14"/>
+      <c r="E30" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="F30" s="14"/>
     </row>
-    <row r="31" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="36">
       <c r="A31" s="14"/>
       <c r="B31" s="14" t="s">
         <v>47</v>
@@ -1262,10 +1321,12 @@
       <c r="D31" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E31" s="14"/>
+      <c r="E31" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="F31" s="14"/>
     </row>
-    <row r="32" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" s="14"/>
       <c r="B32" s="14"/>
       <c r="C32" s="15" t="s">
@@ -1274,10 +1335,12 @@
       <c r="D32" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="14"/>
+      <c r="E32" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="F32" s="14"/>
     </row>
-    <row r="33" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6">
       <c r="A33" s="14"/>
       <c r="B33" s="14"/>
       <c r="C33" s="15" t="s">
@@ -1286,10 +1349,12 @@
       <c r="D33" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="14"/>
+      <c r="E33" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="F33" s="14"/>
     </row>
-    <row r="34" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="A34" s="14"/>
       <c r="B34" s="14"/>
       <c r="C34" s="15" t="s">
@@ -1298,10 +1363,12 @@
       <c r="D34" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="14"/>
+      <c r="E34" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="F34" s="14"/>
     </row>
-    <row r="35" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" s="16" t="s">
         <v>32</v>
       </c>
@@ -1312,10 +1379,12 @@
         <v>89</v>
       </c>
       <c r="D35" s="19"/>
-      <c r="E35" s="17"/>
+      <c r="E35" s="17" t="s">
+        <v>93</v>
+      </c>
       <c r="F35" s="17"/>
     </row>
-    <row r="36" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="36">
       <c r="A36" s="16"/>
       <c r="B36" s="19" t="s">
         <v>86</v>
@@ -1324,10 +1393,12 @@
         <v>90</v>
       </c>
       <c r="D36" s="19"/>
-      <c r="E36" s="17"/>
+      <c r="E36" s="17" t="s">
+        <v>93</v>
+      </c>
       <c r="F36" s="17"/>
     </row>
-    <row r="37" spans="1:6" ht="61" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="54">
       <c r="A37" s="16"/>
       <c r="B37" s="19" t="s">
         <v>87</v>
@@ -1336,10 +1407,12 @@
         <v>91</v>
       </c>
       <c r="D37" s="19"/>
-      <c r="E37" s="17"/>
+      <c r="E37" s="17" t="s">
+        <v>93</v>
+      </c>
       <c r="F37" s="17"/>
     </row>
-    <row r="38" spans="1:6" ht="41" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="36">
       <c r="A38" s="16"/>
       <c r="B38" s="19" t="s">
         <v>88</v>
@@ -1348,55 +1421,69 @@
         <v>92</v>
       </c>
       <c r="D38" s="19"/>
-      <c r="E38" s="17"/>
+      <c r="E38" s="17" t="s">
+        <v>93</v>
+      </c>
       <c r="F38" s="17"/>
     </row>
-    <row r="39" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6">
       <c r="A39" s="16"/>
       <c r="B39" s="17"/>
       <c r="C39" s="18"/>
       <c r="D39" s="19"/>
-      <c r="E39" s="17"/>
+      <c r="E39" s="17" t="s">
+        <v>93</v>
+      </c>
       <c r="F39" s="17"/>
     </row>
-    <row r="40" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6">
       <c r="A40" s="16"/>
       <c r="B40" s="17"/>
       <c r="C40" s="18"/>
       <c r="D40" s="19"/>
-      <c r="E40" s="17"/>
+      <c r="E40" s="17" t="s">
+        <v>93</v>
+      </c>
       <c r="F40" s="17"/>
     </row>
-    <row r="41" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6">
       <c r="A41" s="16"/>
       <c r="B41" s="17"/>
       <c r="C41" s="18"/>
       <c r="D41" s="19"/>
-      <c r="E41" s="17"/>
+      <c r="E41" s="17" t="s">
+        <v>93</v>
+      </c>
       <c r="F41" s="17"/>
     </row>
-    <row r="42" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6">
       <c r="A42" s="16"/>
       <c r="B42" s="17"/>
       <c r="C42" s="18"/>
       <c r="D42" s="19"/>
-      <c r="E42" s="17"/>
+      <c r="E42" s="17" t="s">
+        <v>93</v>
+      </c>
       <c r="F42" s="17"/>
     </row>
-    <row r="43" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6">
       <c r="A43" s="16"/>
       <c r="B43" s="17"/>
       <c r="C43" s="18"/>
       <c r="D43" s="19"/>
-      <c r="E43" s="17"/>
+      <c r="E43" s="17" t="s">
+        <v>93</v>
+      </c>
       <c r="F43" s="17"/>
     </row>
-    <row r="44" spans="1:6" ht="21" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6">
       <c r="A44" s="16"/>
       <c r="B44" s="17"/>
       <c r="C44" s="18"/>
       <c r="D44" s="19"/>
-      <c r="E44" s="17"/>
+      <c r="E44" s="17" t="s">
+        <v>93</v>
+      </c>
       <c r="F44" s="17"/>
     </row>
   </sheetData>
@@ -1408,7 +1495,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E082DBCF-AA86-C145-85E6-2D2B70BF0CB1}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
